--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2768,42 +2768,42 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,52 +3600,52 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,22 +3768,22 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>519.475</t>
+          <t>340.21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-14.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-120.63</t>
+          <t>-121.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>20453719.0</t>
+          <t>13358411.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22489497.2</t>
+          <t>21476259.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21722221.3</t>
+          <t>20896470.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28384455.58</t>
+          <t>28018183.18</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>767275</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1092637.296673307</t>
+          <t>-1316726.695178018</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2067197.58</v>
+        <v>-2549218.39</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>409.169</t>
+          <t>519.475</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.00</t>
+          <t>-9.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>39.77</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.44</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.68</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.08</t>
+          <t>-120.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>151111618.248191</t>
+          <t>150978598.7687861</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16302654.0</t>
+          <t>20453719.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22715830.4</t>
+          <t>22489497.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21471350.7</t>
+          <t>21722221.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28713792.94</t>
+          <t>28384455.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1244479</t>
+          <t>767275</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-915444.5174871245</t>
+          <t>-1092637.296673307</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2064979.52</v>
+        <v>-2067197.58</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-4.34</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,17 +5492,17 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-4.834008229657466</t>
+          <t>-13.67996844119094</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-0.138178351458681</t>
+          <t>-10.11024290164889</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>28.83362772156236</t>
+          <t>24.12947661306339</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.48</t>
+          <t>15.27</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,67 +5750,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-119051.41</v>
+        <v>-158638.12</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,27 +5918,27 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,37 +6181,37 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6221,235 +6221,235 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>11502567.50289017</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-119051.41</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>13.73</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>11515246.17438495</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC14" t="n">
-        <v>57082.84</v>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>-5.198320459977578</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>3.942169776675282</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>10.63449355247814</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>13.85</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>29.59</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>8200</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,47 +6612,47 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -6662,22 +6662,22 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>182277.67</v>
+        <v>57082.84</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>358109.4</v>
+        <v>182277.67</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,27 +7211,27 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>506592.93</v>
+        <v>358109.4</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,42 +7642,42 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>64.814</t>
+          <t>210.912</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-24.20</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,17 +7905,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,59 +7925,59 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-115.01</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2671039.0</t>
+          <t>8506643.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2935559.4</t>
+          <t>4092978.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2666482.7</t>
+          <t>3340460.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3694161.64</t>
+          <t>3784214.54</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-67954.28728605884</t>
+          <t>20437.59198156399</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>80502.61</v>
+        <v>506592.93</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,42 +8073,42 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>57.584</t>
+          <t>64.814</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,72 +8336,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-25.34</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-113.82</t>
+          <t>-114.09</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2344343.0</t>
+          <t>2671039.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2754849.2</t>
+          <t>2935559.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2575191.4</t>
+          <t>2666482.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3723718.0</t>
+          <t>3694161.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>179657</t>
+          <t>269076</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-94946.45114343485</t>
+          <t>-67954.28728605884</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>94170.36</v>
+        <v>80502.61</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,27 +8504,27 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>127.014</t>
+          <t>57.584</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-25.34</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-113.82</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5109455.0</t>
+          <t>2344343.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2737506.0</t>
+          <t>2754849.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2495346.7</t>
+          <t>2575191.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3727977.8</t>
+          <t>3723718.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>242159</t>
+          <t>179657</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-129331.3254756018</t>
+          <t>-94946.45114343485</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>145335.62</v>
+        <v>94170.36</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,42 +8935,42 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>127.014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,102 +9092,102 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9.70</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2024-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2024-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-24.01</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>6.53</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
           <t>-0.75</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.74</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2024-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-23.25</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-0.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,17 +9218,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9238,37 +9238,37 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1833414.0</t>
+          <t>5109455.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2258505.4</t>
+          <t>2737506.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2177041.7</t>
+          <t>2495346.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3675207.8</t>
+          <t>3727977.8</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-179270.7704167048</t>
+          <t>-129331.3254756018</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-83023.7</v>
+        <v>145335.62</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,27 +9366,27 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>66.397</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-22.78</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,22 +9644,22 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9669,39 +9669,39 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-25.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>-0.20</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-110.86</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2719546.0</t>
+          <t>1833414.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2587941.2</t>
+          <t>2258505.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2091542.7</t>
+          <t>2177041.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3730603.22</t>
+          <t>3675207.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>496398</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-196770.2374183902</t>
+          <t>-179270.7704167048</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-55281.78</v>
+        <v>-83023.7</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.766</t>
+          <t>66.397</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>23.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-99.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-22.21</t>
+          <t>-22.78</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,22 +10075,22 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>14.81</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10100,32 +10100,32 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.45999999999999</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>41.85</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>-9.65</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.60</t>
+          <t>-110.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11515246.17438495</t>
+          <t>11502567.50289017</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1767488.0</t>
+          <t>2719546.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2397406.0</t>
+          <t>2587941.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2004228.3</t>
+          <t>2091542.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3769147.72</t>
+          <t>3730603.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>393177</t>
+          <t>496398</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-222495.4111320147</t>
+          <t>-196770.2374183902</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-108618.83</v>
+        <v>-55281.78</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-4.08</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-5.198320459977578</t>
+          <t>-2.61935078269721</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>3.942169776675282</t>
+          <t>-3.587112460302307</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>10.63449355247814</t>
+          <t>8.622558865128855</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,42 +3199,42 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,57 +4026,57 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>519.475</t>
+          <t>340.21</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.04</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>673</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.77</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.44</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-14.13</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-120.63</t>
+          <t>-121.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150978598.7687861</t>
+          <t>150814334.482684</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>20453719.0</t>
+          <t>13358411.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22489497.2</t>
+          <t>21476259.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21722221.3</t>
+          <t>20896470.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28384455.58</t>
+          <t>28018183.18</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>767275</t>
+          <t>579788</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1092637.296673307</t>
+          <t>-1316726.695178018</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2067197.58</v>
+        <v>-2549218.39</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>15.19</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,37 +5750,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5790,32 +5790,32 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-158638.12</v>
+        <v>-195113.6</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,67 +6181,67 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-119051.41</v>
+        <v>-158638.12</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,37 +6612,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6652,235 +6652,235 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>11489558.01298701</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>-119051.41</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>8060</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>11502567.50289017</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC15" t="n">
-        <v>57082.84</v>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>4.92</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>13.73</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>28.92</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>8130</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,47 +7043,47 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>182277.67</v>
+        <v>57082.84</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>358109.4</v>
+        <v>182277.67</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>506592.93</v>
+        <v>358109.4</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>64.814</t>
+          <t>210.912</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-24.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,59 +8356,59 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-115.01</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2671039.0</t>
+          <t>8506643.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2935559.4</t>
+          <t>4092978.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2666482.7</t>
+          <t>3340460.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3694161.64</t>
+          <t>3784214.54</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-67954.28728605884</t>
+          <t>20437.59198156399</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>80502.61</v>
+        <v>506592.93</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57.584</t>
+          <t>64.814</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,177 +8767,177 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>41.24</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>42.06</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-7.65</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-114.09</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/13</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>11489558.01298701</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>2671039.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>2935559.4</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>2666482.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>3694161.64</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>269076</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-67954.28728605884</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>80502.61</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>40.76000000000001</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-25.34</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-113.82</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>11502567.50289017</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>2344343.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2754849.2</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>2575191.4</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>3723718.0</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>179657</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-94946.45114343485</t>
-        </is>
-      </c>
-      <c r="BC20" t="n">
-        <v>94170.36</v>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
       <c r="BM20" t="inlineStr">
         <is>
           <t>-2.61935078269721</t>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>127.014</t>
+          <t>57.584</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-25.34</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-113.82</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5109455.0</t>
+          <t>2344343.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2737506.0</t>
+          <t>2754849.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2495346.7</t>
+          <t>2575191.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3727977.8</t>
+          <t>3723718.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>242159</t>
+          <t>179657</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-129331.3254756018</t>
+          <t>-94946.45114343485</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>145335.62</v>
+        <v>94170.36</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>127.014</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,17 +9649,17 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9669,37 +9669,37 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1833414.0</t>
+          <t>5109455.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2258505.4</t>
+          <t>2737506.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2177041.7</t>
+          <t>2495346.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3675207.8</t>
+          <t>3727977.8</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-179270.7704167048</t>
+          <t>-129331.3254756018</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-83023.7</v>
+        <v>145335.62</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>66.397</t>
+          <t>45.07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,102 +9954,102 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>-0.74</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2024-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2024-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-23.25</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>-0.49</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>23.73</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2024-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2024-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-22.78</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-0.61</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,22 +10075,22 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10100,39 +10100,39 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-25.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.20</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-110.86</t>
+          <t>-111.60</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11502567.50289017</t>
+          <t>11489558.01298701</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2719546.0</t>
+          <t>1833414.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2587941.2</t>
+          <t>2258505.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2091542.7</t>
+          <t>2177041.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3730603.22</t>
+          <t>3675207.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>496398</t>
+          <t>81463</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-196770.2374183902</t>
+          <t>-179270.7704167048</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-55281.78</v>
+        <v>-83023.7</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.73</t>
+          <t>13.61</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1454053.95</v>
+        <v>2130065.67</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.17</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,17 +3610,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3630,42 +3630,42 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,57 +4457,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.44</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>340.21</t>
+          <t>504.24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-14.13</t>
+          <t>-17.47</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-121.38</t>
+          <t>-122.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150814334.482684</t>
+          <t>150691742.176513</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13358411.0</t>
+          <t>19519514.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21476259.0</t>
+          <t>18390851.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20896470.1</t>
+          <t>20228126.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28018183.18</t>
+          <t>28082029.5</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>-1837274</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1316726.695178018</t>
+          <t>-1477356.398321357</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2549218.39</v>
+        <v>-2360819.77</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>15.19</t>
+          <t>14.92</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,42 +5755,42 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -5800,27 +5800,27 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,51 +5830,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>1605800.0</t>
+          <t>2486076.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2958210.36</t>
+          <t>3050572.62</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-195113.6</v>
+        <v>130961.44</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,32 +6186,32 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6221,32 +6221,32 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6261,51 +6261,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-158638.12</v>
+        <v>-195113.6</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,62 +6617,62 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6692,51 +6692,51 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-119051.41</v>
+        <v>-158638.12</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,32 +7048,32 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7083,235 +7083,235 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>11486578.23414985</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-119051.41</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>13.92</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>28.46</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>11489558.01298701</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC16" t="n">
-        <v>57082.84</v>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>13.61</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>8060</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,42 +7479,42 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7524,22 +7524,22 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7554,51 +7554,51 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>182277.67</v>
+        <v>57082.84</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,72 +7910,72 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,51 +7985,51 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>358109.4</v>
+        <v>182277.67</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,72 +8341,72 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,51 +8416,51 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>506592.93</v>
+        <v>358109.4</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64.814</t>
+          <t>210.912</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-24.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,59 +8787,59 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -8847,51 +8847,51 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-115.01</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2671039.0</t>
+          <t>8506643.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2935559.4</t>
+          <t>4092978.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2666482.7</t>
+          <t>3340460.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3694161.64</t>
+          <t>3784214.54</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-67954.28728605884</t>
+          <t>20437.59198156399</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>80502.61</v>
+        <v>506592.93</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.584</t>
+          <t>64.814</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,172 +9203,172 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>41.24</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>41.73</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>42.06</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-7.65</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-114.09</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>11486578.23414985</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>2671039.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>2935559.4</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>2666482.7</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>3694161.64</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>269076</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-67954.28728605884</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>80502.61</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-1.25</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-1.13</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>40.76000000000001</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.75</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-25.34</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-113.82</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/13</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>11489558.01298701</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>2344343.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2754849.2</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>2575191.4</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>3723718.0</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>179657</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-94946.45114343485</t>
-        </is>
-      </c>
-      <c r="BC21" t="n">
-        <v>94170.36</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
       <c r="BM21" t="inlineStr">
         <is>
           <t>-2.61935078269721</t>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>127.014</t>
+          <t>57.584</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,72 +9634,72 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-25.34</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,51 +9709,51 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-113.82</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5109455.0</t>
+          <t>2344343.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2737506.0</t>
+          <t>2754849.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2495346.7</t>
+          <t>2575191.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3727977.8</t>
+          <t>3723718.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>242159</t>
+          <t>179657</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-129331.3254756018</t>
+          <t>-94946.45114343485</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>145335.62</v>
+        <v>94170.36</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.07</t>
+          <t>127.014</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-24.01</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,17 +10080,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10100,37 +10100,37 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,51 +10140,51 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.60</t>
+          <t>-112.95</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/13</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11489558.01298701</t>
+          <t>11486578.23414985</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1833414.0</t>
+          <t>5109455.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2258505.4</t>
+          <t>2737506.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2177041.7</t>
+          <t>2495346.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3675207.8</t>
+          <t>3727977.8</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>81463</t>
+          <t>242159</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-179270.7704167048</t>
+          <t>-129331.3254756018</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-83023.7</v>
+        <v>145335.62</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.61</t>
+          <t>13.92</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>2130065.67</v>
+        <v>1376505.33</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1454053.95</v>
+        <v>2130065.67</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>2478665.68</v>
+        <v>1454053.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>2288252.23</v>
+        <v>2478665.68</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>451260.12</v>
+        <v>2288252.23</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1450493.77</v>
+        <v>451260.12</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-4.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>2419680.25</v>
+        <v>1450493.77</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4061,42 +4061,42 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-977116.87</v>
+        <v>2419680.25</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-702942.96</v>
+        <v>-977116.87</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>857.171</t>
+          <t>700.928</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.62</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>7.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,57 +4888,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.47</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>39.12</t>
+          <t>38.99</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.63</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.31</t>
+          <t>-124.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>33340953.0</t>
+          <t>27244704.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20595050.2</t>
+          <t>22783460.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22030516.7</t>
+          <t>22749645.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28317533.86</t>
+          <t>28438883.58</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1435466</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1424426.538814767</t>
+          <t>-1313429.065286876</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1133312.31</v>
+        <v>-702942.96</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>504.24</t>
+          <t>857.171</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.20</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>776</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.12</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-17.47</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-122.36</t>
+          <t>-123.31</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150691742.176513</t>
+          <t>150535732.3834532</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19519514.0</t>
+          <t>33340953.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>18390851.8</t>
+          <t>20595050.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20228126.1</t>
+          <t>22030516.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28082029.5</t>
+          <t>28317533.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1837274</t>
+          <t>-1435466</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1477356.398321357</t>
+          <t>-1424426.538814767</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-2360819.77</v>
+        <v>-1133312.31</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>15.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,67 +5750,67 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2486076.8</t>
+          <t>2685328.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3050572.62</t>
+          <t>3081600.88</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>130961.44</v>
+        <v>102999.8</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,47 +6181,47 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -6231,27 +6231,27 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>1605800.0</t>
+          <t>2486076.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>2958210.36</t>
+          <t>3050572.62</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-195113.6</v>
+        <v>130961.44</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,37 +6612,37 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6652,32 +6652,32 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-158638.12</v>
+        <v>-195113.6</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,67 +7043,67 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-119051.41</v>
+        <v>-158638.12</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,37 +7474,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7514,235 +7514,235 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>11476328.17769784</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-119051.41</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>13.73</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>28.82</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>11486578.23414985</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC17" t="n">
-        <v>57082.84</v>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>28.46</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>8240</t>
-        </is>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,47 +7905,47 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -7955,22 +7955,22 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>182277.67</v>
+        <v>57082.84</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,102 +8230,102 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>-1.18</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>13.94</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2024-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2024-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-23.06</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>-0.49</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>30.81</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2024-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2024-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>-23.44</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>0.62</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>358109.4</v>
+        <v>182277.67</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>506592.93</v>
+        <v>358109.4</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>64.814</t>
+          <t>210.912</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-24.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,59 +9218,59 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-115.01</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2671039.0</t>
+          <t>8506643.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2935559.4</t>
+          <t>4092978.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2666482.7</t>
+          <t>3340460.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3694161.64</t>
+          <t>3784214.54</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-67954.28728605884</t>
+          <t>20437.59198156399</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>80502.61</v>
+        <v>506592.93</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.584</t>
+          <t>64.814</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-22.02</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,72 +9629,72 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>42.53</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.24</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.34</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.82</t>
+          <t>-114.09</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2344343.0</t>
+          <t>2671039.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2754849.2</t>
+          <t>2935559.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2575191.4</t>
+          <t>2666482.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3723718.0</t>
+          <t>3694161.64</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>179657</t>
+          <t>269076</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-94946.45114343485</t>
+          <t>-67954.28728605884</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>94170.36</v>
+        <v>80502.61</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>41.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>40.4</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>127.014</t>
+          <t>57.584</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.01</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>55.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-25.34</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.95</t>
+          <t>-113.82</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11486578.23414985</t>
+          <t>11476328.17769784</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5109455.0</t>
+          <t>2344343.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2737506.0</t>
+          <t>2754849.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2495346.7</t>
+          <t>2575191.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3727977.8</t>
+          <t>3723718.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>242159</t>
+          <t>179657</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-129331.3254756018</t>
+          <t>-94946.45114343485</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>145335.62</v>
+        <v>94170.36</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>13.92</t>
+          <t>13.73</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.82</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,280 +1014,280 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/23</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>150693340.205165</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>6.78</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>15.25</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>11850</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>150408451.7952586</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,62 +2773,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,17 +4953,17 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -4973,42 +4973,42 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-977116.8664098568</t>
+          <t>2419680.246381927</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>19337957</v>
+        <v>66861836</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>700.928</t>
+          <t>499.552</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.97</t>
+          <t>-4.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.50</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.47</t>
+          <t>5.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>38.99</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.63</t>
+          <t>41.54</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.03</t>
+          <t>-124.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150408451.7952586</t>
+          <t>150693340.205165</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27244704.0</t>
+          <t>19337957.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22783460.2</t>
+          <t>22560307.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22749645.3</t>
+          <t>22524902.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28438883.58</t>
+          <t>28140249.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1313429.065286876</t>
+          <t>-1261688.726998104</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-702942.9608834758</t>
+          <t>-977116.8664098568</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>27244704</v>
+        <v>19337957</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-6.87</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.23</t>
+          <t>15.25</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>11850</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,79 +5810,79 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3005486.0</t>
+          <t>2863240.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3080321.22</t>
+          <t>3003536.14</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>2352112</v>
+        <v>1116507</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,72 +6246,72 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2685328.4</t>
+          <t>3005486.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3081600.88</t>
+          <t>3080321.22</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>2908526</v>
+        <v>2352112</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,67 +6682,67 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2486076.8</t>
+          <t>2685328.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3050572.62</t>
+          <t>3081600.88</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>6281061</v>
+        <v>2908526</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,47 +7118,47 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -7168,27 +7168,27 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>1605800.0</t>
+          <t>2486076.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2958210.36</t>
+          <t>3050572.62</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>1657994</v>
+        <v>6281061</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,37 +7554,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7594,32 +7594,32 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1827737</v>
+        <v>1657994</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,67 +7990,67 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>751324</v>
+        <v>1827737</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,37 +8426,37 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8466,240 +8466,240 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>11450862.2840746</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-119051.4083294612</t>
+        </is>
+      </c>
+      <c r="BD19" t="n">
+        <v>751324</v>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>4.93</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>13.72</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>28.89</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>8120</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>11464908.40732759</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>57082.84207214369</t>
-        </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>1912268</v>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>4.95</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>13.65</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,47 +8862,47 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -8912,22 +8912,22 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>182277.6697147163</t>
+          <t>57082.84207214369</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1879677</v>
+        <v>1912268</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>358109.3995714383</t>
+          <t>182277.6697147163</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>2718884</v>
+        <v>1879677</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>506592.9279534896</t>
+          <t>358109.3995714383</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>8506643</v>
+        <v>2718884</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>64.814</t>
+          <t>210.912</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-22.02</t>
+          <t>-24.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,17 +10170,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10190,59 +10190,59 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-24.56</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-114.09</t>
+          <t>-115.01</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11464908.40732759</t>
+          <t>11450862.2840746</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2671039.0</t>
+          <t>8506643.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2935559.4</t>
+          <t>4092978.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2666482.7</t>
+          <t>3340460.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3694161.64</t>
+          <t>3784214.54</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>269076</t>
+          <t>752518</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-67954.28728605884</t>
+          <t>20437.59198156399</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>80502.61392950919</t>
+          <t>506592.9279534896</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2671039</v>
+        <v>8506643</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-6.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.48</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,56 +1094,56 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>74142370.0</t>
+          <t>77102277.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>34130931.06</t>
+          <t>33864219.92</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>232650449</v>
+        <v>39561838</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,280 +1450,280 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>150562465.4441261</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>6.56</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>15.74</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>12236</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/23</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>150693340.205165</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>15.25</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>11850</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,102 +3088,102 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-08-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-03-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>44.3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>43.15</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-14.83</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-15.62</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>-1.09</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-08-15 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-03-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>43.15</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>54.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-14.37</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-15.62</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>499.552</t>
+          <t>1764.112</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-12.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>18.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,17 +5389,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5409,42 +5409,42 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>39.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.54</t>
+          <t>41.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-18.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-124.74</t>
+          <t>-125.95</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/23</t>
+          <t>2025/11/25</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150693340.205165</t>
+          <t>150562465.4441261</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19337957.0</t>
+          <t>66861836.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22560307.8</t>
+          <t>33260992.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22524902.5</t>
+          <t>27368625.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28140249.02</t>
+          <t>28716017.48</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>5892366</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1261688.726998104</t>
+          <t>-695324.269555022</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-977116.8664098568</t>
+          <t>2419680.246381927</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>19337957</v>
+        <v>66861836</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-6.87</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.25</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11850</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,37 +5810,37 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5850,32 +5850,32 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2863240.0</t>
+          <t>2771491.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3003536.14</t>
+          <t>2927231.58</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1116507</v>
+        <v>1199250</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,217 +6246,217 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
+          <t>5.81</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-114.37</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>11437034.22206304</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>1116507.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>2863240.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>2340609.0</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>3003536.14</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>522631</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>6871.849786184752</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-99243.2136227577</t>
+        </is>
+      </c>
+      <c r="BD14" t="n">
+        <v>1116507</v>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>-5.36</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
           <t>4.91</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-114.58</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>11450862.2840746</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>2352112.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>3005486.0</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>3079622.6</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>3080321.22</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-74136</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>26165.49767871974</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>39120.61030571489</t>
-        </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>2352112</v>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>-5.83</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
       <c r="BU14" t="inlineStr">
         <is>
           <t>23.89</t>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,72 +6682,72 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2685328.4</t>
+          <t>3005486.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3081600.88</t>
+          <t>3080321.22</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2908526</v>
+        <v>2352112</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,67 +7118,67 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2486076.8</t>
+          <t>2685328.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3050572.62</t>
+          <t>3081600.88</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>6281061</v>
+        <v>2908526</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,47 +7554,47 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -7604,27 +7604,27 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>1605800.0</t>
+          <t>2486076.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>2958210.36</t>
+          <t>3050572.62</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>1657994</v>
+        <v>6281061</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,37 +7990,37 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -8030,32 +8030,32 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1827737</v>
+        <v>1657994</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,67 +8426,67 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>751324</v>
+        <v>1827737</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,37 +8862,37 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8902,240 +8902,240 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>11437034.22206304</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-119051.4083294612</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
+        <v>751324</v>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>4.91</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>13.75</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>8140</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>11450862.2840746</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>57082.84207214369</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>1912268</v>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>4.93</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>13.72</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>28.89</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>8120</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,47 +9298,47 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -9348,22 +9348,22 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>182277.6697147163</t>
+          <t>57082.84207214369</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1879677</v>
+        <v>1912268</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>358109.3995714383</t>
+          <t>182277.6697147163</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>2718884</v>
+        <v>1879677</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>210.912</t>
+          <t>67.446</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-24.20</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.30</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
           <t>-1.28</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>-1.29</t>
-        </is>
-      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.13</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.66</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.03</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-24.56</t>
+          <t>-21.99</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.01</t>
+          <t>-115.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11450862.2840746</t>
+          <t>11437034.22206304</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8506643.0</t>
+          <t>2718884.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>4092978.8</t>
+          <t>4270072.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3340460.0</t>
+          <t>3264289.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3784214.54</t>
+          <t>3809181.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>752518</t>
+          <t>1005783</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20437.59198156399</t>
+          <t>72387.10084154466</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>506592.9279534896</t>
+          <t>358109.3995714383</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>8506643</v>
+        <v>2718884</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.53</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,64 +1029,64 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>38.11</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>77102277.8</t>
+          <t>75499582.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>33864219.92</t>
+          <t>33454972.78</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>39561838</v>
+        <v>35810040</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>38.11</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>74142370.0</t>
+          <t>77102277.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>34130931.06</t>
+          <t>33864219.92</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>232650449</v>
+        <v>39561838</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,280 +1886,280 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>38.22</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>40.17</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>150423914.0772532</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>74142370.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>34130931.06</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>232650449</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>29.71</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>150562465.4441261</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>41298962</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>6.56</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>15.74</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>12236</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.41</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>37871124.0</t>
+          <t>35487232.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>29545425.32</t>
+          <t>29950115.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>28176624</v>
+        <v>41298962</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,12 +2580,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36085517.8</t>
+          <t>37871124.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>29409986.0</t>
+          <t>29545425.32</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>43823516</v>
+        <v>28176624</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>31929308.6</t>
+          <t>36085517.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>29130934.74</t>
+          <t>29409986.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>24762299</v>
+        <v>43823516</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>40349216.0</t>
+          <t>31929308.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>29061426.18</t>
+          <t>29130934.74</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>39374759</v>
+        <v>24762299</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>36341855.6</t>
+          <t>40349216.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>28846965.04</t>
+          <t>29061426.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>53218422</v>
+        <v>39374759</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>41.17</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>31147112.0</t>
+          <t>36341855.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>28091032.78</t>
+          <t>28846965.04</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>19248593</v>
+        <v>53218422</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>41.17</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33965584.0</t>
+          <t>31147112.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>28206383.42</t>
+          <t>28091032.78</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>23042470</v>
+        <v>19248593</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1764.112</t>
+          <t>605.721</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.75</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.80</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>915</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.95</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>39.69</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>41.67</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.69</t>
+          <t>-16.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.95</t>
+          <t>-127.09</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150562465.4441261</t>
+          <t>150423914.0772532</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>66861836.0</t>
+          <t>23042470.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>33260992.8</t>
+          <t>33965584.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27368625.9</t>
+          <t>26178217.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>28716017.48</t>
+          <t>28206383.42</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5892366</t>
+          <t>7787366</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-695324.269555022</t>
+          <t>-365198.417442461</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2419680.246381927</t>
+          <t>1450493.769176625</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>66861836</v>
+        <v>23042470</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-114.03</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>2771491.2</t>
+          <t>1890196.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2188645.6</t>
+          <t>2188136.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>2927231.58</t>
+          <t>2880265.04</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>-297940</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-23017.83249355435</t>
+          <t>-49290.9417857567</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-187411.0850321194</t>
+          <t>-193793.0428928696</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>1199250</v>
+        <v>1874587</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,102 +6140,102 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>26.63</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-02-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-03-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2024-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2024-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>54.1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>52.9</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>53.0</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-23.06</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>0.25</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>22.33</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-02-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-03-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2024-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2024-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>54.1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>52.9</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-23.25</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>0.13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,37 +6246,37 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -6286,32 +6286,32 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>40.84</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>2863240.0</t>
+          <t>2771491.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3003536.14</t>
+          <t>2927231.58</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>1116507</v>
+        <v>1199250</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,79 +6682,79 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>40.89</t>
+          <t>40.84</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3005486.0</t>
+          <t>2863240.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3080321.22</t>
+          <t>3003536.14</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2352112</v>
+        <v>1116507</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,72 +7118,72 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.89</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>41.47</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2685328.4</t>
+          <t>3005486.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>3081600.88</t>
+          <t>3080321.22</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2908526</v>
+        <v>2352112</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,67 +7554,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.47</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2486076.8</t>
+          <t>2685328.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>3050572.62</t>
+          <t>3081600.88</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>6281061</v>
+        <v>2908526</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,47 +7990,47 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -8040,27 +8040,27 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1605800.0</t>
+          <t>2486076.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>2958210.36</t>
+          <t>3050572.62</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>1657994</v>
+        <v>6281061</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,37 +8426,37 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8466,32 +8466,32 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.97</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>1817978.0</t>
+          <t>1605800.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2948865.1</t>
+          <t>2958210.36</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>1827737</v>
+        <v>1657994</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,67 +8862,67 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41.59</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3153759.2</t>
+          <t>1817978.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2999862.66</t>
+          <t>2948865.1</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>751324</v>
+        <v>1827737</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,37 +9298,37 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9338,240 +9338,240 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
+          <t>41.06</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>41.59</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>41.98</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.25</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-116.01</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>11424694.94635193</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>3153759.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>3044659.3</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>2999862.66</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>109099</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>53047.22080488506</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-119051.4083294612</t>
+        </is>
+      </c>
+      <c r="BD21" t="n">
+        <v>751324</v>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>13.85</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>29.71</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>8200</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>中鋼構-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
           <t>41.1</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-116.40</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>11437034.22206304</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>1912268.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>3146275.7</t>
-        </is>
-      </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>391426</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>84337.88064749347</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>57082.84207214369</t>
-        </is>
-      </c>
-      <c r="BD21" t="n">
-        <v>1912268</v>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>4.91</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>13.75</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>8140</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>工程91.33%、商品銷售5.82%、勞務2.74%、其他0.11% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>中鋼構-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,47 +9734,47 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -9784,22 +9784,22 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3624117.2</t>
+          <t>3537702.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>3818341.1</t>
+          <t>3826669.38</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>182277.6697147163</t>
+          <t>57082.84207214369</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1879677</v>
+        <v>1912268</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>67.446</t>
+          <t>46.124</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>52.17</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>41.13</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.03</t>
+          <t>42.01</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-21.99</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.89</t>
+          <t>-116.46</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11437034.22206304</t>
+          <t>11424694.94635193</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2718884.0</t>
+          <t>1879677.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>4270072.8</t>
+          <t>3624117.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3264289.1</t>
+          <t>3180811.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>3809181.22</t>
+          <t>3818341.1</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1005783</t>
+          <t>443305</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>72387.10084154466</t>
+          <t>89293.34220664798</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>358109.3995714383</t>
+          <t>182277.6697147163</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2718884</v>
+        <v>1879677</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>41.0</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>40.6</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.47</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>40.03</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>40.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>35810040.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>75499582.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>75499582.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>55792550.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>33454972.78</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>33454972.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>7886638.29228013</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>35810040</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>35810040.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>36.87</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>40.07</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>40.07</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>39561838.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>77102277.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>77102277.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>54515793.2</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>33864219.92</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>33864219.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>11730479.54280426</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>39561838</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>39561838.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>36.60000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>40.17</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40.17</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>232650449.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>74142370.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>74142370</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>57245793.0</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>34130931.06</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>34130931.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>16400757.27416717</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>232650449</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>36.61</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>38.41</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>40.3</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>41298962.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>35487232.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>35487232</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>35914543.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>29950115.64</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>29950115.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>1798775.809179619</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>41298962</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>41298962.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>40.43</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>40.43</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>28176624.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>37871124.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>37871124</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>34509118.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>29545425.32</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>29545425.32</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1376505.330298137</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>28176624</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>28176624.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>37.07000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>40.58</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40.58</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>43823516.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>36085517.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>36085517.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>35025550.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>29409986.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>29409986</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>2130065.670099653</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>43823516</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>43823516.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>37.47000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>24762299.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>31929308.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>31929308.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>32595150.7</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>29130934.74</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>29130934.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1454053.953026839</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>24762299</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>24762299.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>37.65000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>39.23</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>39.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>39374759.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>40349216.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>40349216</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>31454761.9</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>29061426.18</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>29061426.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>2478665.680314712</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>39374759</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>39374759.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>37.99</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>39.42</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>41.05</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>41.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>53218422.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>36341855.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>36341855.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>29562657.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>28846965.04</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>28846965.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2288252.230714723</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>53218422</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>53218422.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>38.31</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>19248593.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>31147112.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>31147112</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>25871081.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>28091032.78</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>28091032.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>451260.1159035005</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>19248593</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>19248593.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>38.46</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>39.69</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>41.29</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>41.29</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>23042470.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>33965584.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>33965584</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>26178217.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>28206383.42</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>28206383.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>1450493.769176625</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>23042470</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>23042470.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>40.67</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>40.77</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>41.35</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>41.35</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>1874587.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>1890196.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>1890196.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2188136.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2880265.04</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2880265.04</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-193793.0428928696</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>1874587</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1874587.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>40.71</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>40.8</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>41.37</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.37</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>1199250.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2771491.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2771491.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2188645.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2927231.58</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2927231.58</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-187411.0850321194</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>1199250</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1199250.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>40.63</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>40.84</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>41.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>40.84</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1116507.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2863240.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2863240</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2340609.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>3003536.14</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>3003536.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-99243.2136227577</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1116507</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1116507.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>40.64</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>40.89</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>41.43</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>41.43</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2352112.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3005486.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3005486</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3079622.6</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>3080321.22</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>3080321.22</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>39120.61030571489</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2352112</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2352112.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>40.76000000000001</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>40.94</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.47</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.47</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2908526.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2685328.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2685328.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3111515.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>3081600.88</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>3081600.88</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>102999.801264043</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2908526</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2908526.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>40.85</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>40.97</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>6281061.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2486076.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2486076.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3055097.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>3050572.62</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>3050572.62</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>130961.438302224</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>6281061</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>6281061.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>40.75</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>40.97</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.53</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>40.97</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.53</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>1657994.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>1605800.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>1605800</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2937936.4</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2958210.36</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2958210.36</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-195113.5958683104</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>1657994</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1657994.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>40.79000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>41.03</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.57</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1827737.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>1817978.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>1817978</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2955478.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2948865.1</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2948865.1</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-158638.1234023483</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1827737</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1827737.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>40.68</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>41.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.59</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>41.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.59</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>751324.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3153759.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3153759.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3044659.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2999862.66</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2999862.66</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-119051.4083294612</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>751324</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>751324.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>40.73</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.61</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.61</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>1912268.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>3537702.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>3537702.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3146275.7</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>3826669.38</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>3826669.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>57082.84207214369</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>1912268</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1912268.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>40.71</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>41.1</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.64</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.64</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1879677.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>3624117.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>3624117.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3180811.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>3818341.1</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>3818341.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>182277.6697147163</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1879677</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1879677.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,60 +1459,60 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.63</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,274 +2304,274 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>150251779.8621429</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>12557</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>150423914.0772532</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>29.71</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.58</v>
+        <v>39.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.17</v>
+        <v>41.05</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>31147112</v>
+        <v>36341855.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>28091032.78</v>
+        <v>28846965.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>605.721</t>
+          <t>504.317</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>511</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>21.95</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>16.69</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.69</v>
+        <v>39.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.29</v>
+        <v>41.17</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.67</t>
+          <t>41.64</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.76</t>
+          <t>-13.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-127.09</t>
+          <t>-128.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150423914.0772532</t>
+          <t>150251779.8621429</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>33965584</v>
+        <v>31147112</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>26178217.9</t>
+          <t>25871081.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>28206383.42</v>
+        <v>28091032.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7787366</t>
+          <t>5276030</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-365198.417442461</t>
+          <t>-239589.4123123131</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1450493.769176625</t>
+          <t>451260.1159035005</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>23042470.0</t>
+          <t>19248593.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.809</t>
+          <t>224.845</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-20.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,68 +5749,68 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.77</v>
+        <v>40.8</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-111.41</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>1890196.4</v>
+        <v>3205574.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2188136.6</t>
+          <t>2945451.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>2880265.04</v>
+        <v>3037945.7</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-297940</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-49290.9417857567</t>
+          <t>16353.29351619472</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-193793.0428928696</t>
+          <t>377396.5876769274</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,68 +6179,68 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.8</v>
+        <v>40.77</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.37</v>
+        <v>41.35</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-114.03</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2771491.2</v>
+        <v>1890196.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2188645.6</t>
+          <t>2188136.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2927231.58</v>
+        <v>2880265.04</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>-297940</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-23017.83249355435</t>
+          <t>-49290.9417857567</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-187411.0850321194</t>
+          <t>-193793.0428928696</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,32 +6609,32 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -6644,28 +6644,28 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.4</v>
+        <v>41.37</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2863240</v>
+        <v>2771491.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3003536.14</v>
+        <v>2927231.58</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,70 +7039,70 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.43</v>
+        <v>41.4</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3005486</v>
+        <v>2863240</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3080321.22</v>
+        <v>3003536.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,63 +7469,63 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.94</v>
+        <v>40.89</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.47</v>
+        <v>41.43</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2685328.4</v>
+        <v>3005486</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3081600.88</v>
+        <v>3080321.22</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,58 +7899,58 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.97</v>
+        <v>40.94</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2486076.8</v>
+        <v>2685328.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3050572.62</v>
+        <v>3081600.88</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8183,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM19" t="n">
         <v>40.97</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.53</v>
+        <v>41.5</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>1605800</v>
+        <v>2486076.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>2958210.36</v>
+        <v>3050572.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,32 +8759,32 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8794,28 +8794,28 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>41.03</v>
+        <v>40.97</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.57</v>
+        <v>41.53</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1817978</v>
+        <v>1605800</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2948865.1</v>
+        <v>2958210.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,58 +9189,58 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.06</v>
+        <v>41.03</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.59</v>
+        <v>41.57</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3153759.2</v>
+        <v>1817978</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2999862.66</v>
+        <v>2948865.1</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,32 +9619,32 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9654,33 +9654,33 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.1</v>
+        <v>41.06</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.61</v>
+        <v>41.59</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-116.40</t>
+          <t>-116.01</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1912268.0</t>
+          <t>751324.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3537702.2</v>
+        <v>3153759.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3146275.7</t>
+          <t>3044659.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>3826669.38</v>
+        <v>2999862.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>391426</t>
+          <t>109099</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>84337.88064749347</t>
+          <t>53047.22080488506</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>57082.84207214369</t>
+          <t>-119051.4083294612</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1912268.0</t>
+          <t>751324.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.124</t>
+          <t>46.612</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>12.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,63 +10049,63 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>225</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>86.96</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>56.63</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>41.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.64</v>
+        <v>41.61</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-116.46</t>
+          <t>-116.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11424694.94635193</t>
+          <t>11428699.845</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3624117.2</v>
+        <v>3537702.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3180811.6</t>
+          <t>3146275.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>3818341.1</v>
+        <v>3826669.38</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>443305</t>
+          <t>391426</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>89293.34220664798</t>
+          <t>84337.88064749347</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>182277.6697147163</t>
+          <t>57082.84207214369</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1879677.0</t>
+          <t>1912268.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>13.85</t>
+          <t>14.19</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>492.79</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>510.601</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,60 +1889,60 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.63</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,274 +2734,274 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>150078431.9122682</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>6.43</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>16.07</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>29.63</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>12493</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>150251779.8621429</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>6.39</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>12557</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN11" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>504.317</t>
+          <t>1408.733</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>22.93</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>493</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>37.99</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.58</v>
+        <v>39.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.17</v>
+        <v>41.05</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.64</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-13.76</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.06</t>
+          <t>-129.19</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150251779.8621429</t>
+          <t>150078431.9122682</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>31147112</v>
+        <v>36341855.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>25871081.1</t>
+          <t>29562657.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>28091032.78</v>
+        <v>28846965.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5276030</t>
+          <t>6779197</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-239589.4123123131</t>
+          <t>149309.3019995387</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>451260.1159035005</t>
+          <t>2288252.230714723</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>19248593.0</t>
+          <t>53218422.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>224.845</t>
+          <t>113.221</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-20.60</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.8</v>
+        <v>40.86</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>134.89</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-111.41</t>
+          <t>-108.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3205574.4</v>
+        <v>3689547.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2945451.4</t>
+          <t>3347516.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3037945.7</v>
+        <v>3114730.64</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>260123</t>
+          <t>342030</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>16353.29351619472</t>
+          <t>77573.77364968196</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>377396.5876769274</t>
+          <t>414286.4143838617</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.809</t>
+          <t>224.845</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-20.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.77</v>
+        <v>40.8</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-111.41</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>1890196.4</v>
+        <v>3205574.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2188136.6</t>
+          <t>2945451.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>2880265.04</v>
+        <v>3037945.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-297940</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-49290.9417857567</t>
+          <t>16353.29351619472</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-193793.0428928696</t>
+          <t>377396.5876769274</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,239 +6604,239 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>51.85</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-0.24</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>40.67</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>41.77</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>21.72</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-113.30</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>11422607.49714693</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>1874587.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>1890196.4</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>2188136.6</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2880265.04</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-297940</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-49290.9417857567</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-193793.0428928696</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1874587.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>-4.43</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>中鋼構</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-2.61935078269721</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>-3.587112460302307</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>8.622558865128855</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>4.72</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>5.20%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>3.24%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
           <t>29.63</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>40.71</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>41.79</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>9.78</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.24</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-114.03</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>11428699.845</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>1199250.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>2771491.2</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>2188645.6</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2927231.58</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>582845</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-23017.83249355435</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-187411.0850321194</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>1199250.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>42.9</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/07/25</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>-5.13</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>中鋼構</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-2.61935078269721</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>-3.587112460302307</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>8.622558865128855</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>14.19</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>5.20%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>3.24%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>29.67</t>
-        </is>
-      </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,37 +7034,37 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -7074,28 +7074,28 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.4</v>
+        <v>41.37</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2863240</v>
+        <v>2771491.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3003536.14</v>
+        <v>2927231.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,75 +7464,75 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.43</v>
+        <v>41.4</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3005486</v>
+        <v>2863240</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3080321.22</v>
+        <v>3003536.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,68 +7894,68 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.94</v>
+        <v>40.89</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.47</v>
+        <v>41.43</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2685328.4</v>
+        <v>3005486</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3081600.88</v>
+        <v>3080321.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,63 +8324,63 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.97</v>
+        <v>40.94</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>2486076.8</v>
+        <v>2685328.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3050572.62</v>
+        <v>3081600.88</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8613,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM20" t="n">
         <v>40.97</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.53</v>
+        <v>41.5</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>1605800</v>
+        <v>2486076.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>2958210.36</v>
+        <v>3050572.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,37 +9184,37 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -9224,28 +9224,28 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>41.03</v>
+        <v>40.97</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.57</v>
+        <v>41.53</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1817978</v>
+        <v>1605800</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2948865.1</v>
+        <v>2958210.36</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,63 +9614,63 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.06</v>
+        <v>41.03</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.59</v>
+        <v>41.57</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3153759.2</v>
+        <v>1817978</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2999862.66</v>
+        <v>2948865.1</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.612</t>
+          <t>18.293</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,37 +10044,37 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>113</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>86.96</t>
+          <t>78.26</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10084,33 +10084,33 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.1</v>
+        <v>41.06</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.61</v>
+        <v>41.59</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-116.40</t>
+          <t>-116.01</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11428699.845</t>
+          <t>11422607.49714693</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1912268.0</t>
+          <t>751324.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3537702.2</v>
+        <v>3153759.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3146275.7</t>
+          <t>3044659.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>3826669.38</v>
+        <v>2999862.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>391426</t>
+          <t>109099</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>84337.88064749347</t>
+          <t>53047.22080488506</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>57082.84207214369</t>
+          <t>-119051.4083294612</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1912268.0</t>
+          <t>751324.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>14.19</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,60 +2319,60 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,274 +3164,274 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>149902651.9038461</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>16.03</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>12460</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>150078431.9122682</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.43</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>16.07</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>29.63</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>12493</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1408.733</t>
+          <t>1065.248</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-14.37</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>11.35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.69</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.63</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.99</t>
+          <t>37.65000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.42</v>
+        <v>39.23</v>
       </c>
       <c r="AN12" t="n">
-        <v>41.05</v>
+        <v>40.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-18.37</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-129.19</t>
+          <t>-130.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>150078431.9122682</t>
+          <t>149902651.9038461</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>36341855.6</v>
+        <v>40349216</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>29562657.9</t>
+          <t>31454761.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>28846965.04</v>
+        <v>29061426.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6779197</t>
+          <t>8894454</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>149309.3019995387</t>
+          <t>507671.8217403347</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2288252.230714723</t>
+          <t>2478665.680314712</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>53218422.0</t>
+          <t>39374759.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-10.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.03</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>113.221</t>
+          <t>154.296</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,39 +5759,39 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>41.68000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.86</v>
+        <v>40.93</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.35</v>
+        <v>41.36</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5800,17 +5800,17 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>134.89</t>
+          <t>260.45</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-108.53</t>
+          <t>-105.17</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>3689547.2</v>
+        <v>4776685.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3347516.6</t>
+          <t>3819962.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3114730.64</v>
+        <v>3197880.56</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>342030</t>
+          <t>956722</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>77573.77364968196</t>
+          <t>152296.0942757491</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>414286.4143838617</t>
+          <t>563268.8577191187</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>224.845</t>
+          <t>113.221</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-20.60</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.8</v>
+        <v>40.86</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>134.89</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-111.41</t>
+          <t>-108.53</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3205574.4</v>
+        <v>3689547.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>2945451.4</t>
+          <t>3347516.6</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3037945.7</v>
+        <v>3114730.64</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>260123</t>
+          <t>342030</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>16353.29351619472</t>
+          <t>77573.77364968196</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>377396.5876769274</t>
+          <t>414286.4143838617</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.809</t>
+          <t>224.845</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-20.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.77</v>
+        <v>40.8</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-111.41</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>1890196.4</v>
+        <v>3205574.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2188136.6</t>
+          <t>2945451.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>2880265.04</v>
+        <v>3037945.7</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-297940</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-49290.9417857567</t>
+          <t>16353.29351619472</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-193793.0428928696</t>
+          <t>377396.5876769274</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.8</v>
+        <v>40.77</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.37</v>
+        <v>41.35</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.03</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2771491.2</v>
+        <v>1890196.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2188645.6</t>
+          <t>2188136.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2927231.58</v>
+        <v>2880265.04</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>-297940</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-23017.83249355435</t>
+          <t>-49290.9417857567</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-187411.0850321194</t>
+          <t>-193793.0428928696</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,37 +7464,37 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -7504,28 +7504,28 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.4</v>
+        <v>41.37</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2863240</v>
+        <v>2771491.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3003536.14</v>
+        <v>2927231.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,75 +7894,75 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.43</v>
+        <v>41.4</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>3005486</v>
+        <v>2863240</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3080321.22</v>
+        <v>3003536.14</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,68 +8324,68 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.94</v>
+        <v>40.89</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.47</v>
+        <v>41.43</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>2685328.4</v>
+        <v>3005486</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3081600.88</v>
+        <v>3080321.22</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,63 +8754,63 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.97</v>
+        <v>40.94</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>2486076.8</v>
+        <v>2685328.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3050572.62</v>
+        <v>3081600.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM21" t="n">
         <v>40.97</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.53</v>
+        <v>41.5</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1605800</v>
+        <v>2486076.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>2958210.36</v>
+        <v>3050572.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,37 +9614,37 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -9654,28 +9654,28 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>41.03</v>
+        <v>40.97</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.57</v>
+        <v>41.53</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1817978</v>
+        <v>1605800</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2948865.1</v>
+        <v>2958210.36</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.293</t>
+          <t>44.771</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,63 +10044,63 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>78.26</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>40.79000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.06</v>
+        <v>41.03</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.59</v>
+        <v>41.57</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-116.01</t>
+          <t>-115.72</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11422607.49714693</t>
+          <t>11420336.4017094</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3153759.2</v>
+        <v>1817978</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3044659.3</t>
+          <t>2955478.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2999862.66</v>
+        <v>2948865.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>109099</t>
+          <t>-1137500</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>53047.22080488506</t>
+          <t>20480.24477300301</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-119051.4083294612</t>
+          <t>-158638.1234023483</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>751324.0</t>
+          <t>1827737.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>41.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN5" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,60 +2749,60 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,274 +3594,274 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>149719452.0704125</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.44</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>16.05</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>30.23</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>12477</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>149902651.9038461</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>6.44</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>16.03</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>30.23</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>12460</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN9" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1065.248</t>
+          <t>672.504</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.37</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>363</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-3.97</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.65000000000001</t>
+          <t>37.47000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.23</v>
+        <v>39.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.9</v>
+        <v>40.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-18.37</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-130.59</t>
+          <t>-132.14</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>149902651.9038461</t>
+          <t>149719452.0704125</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>40349216</v>
+        <v>31929308.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>31454761.9</t>
+          <t>32595150.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>29061426.18</v>
+        <v>29130934.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>8894454</t>
+          <t>-665842</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>507671.8217403347</t>
+          <t>653269.0727074891</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2478665.680314712</t>
+          <t>1454053.953026839</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>39374759.0</t>
+          <t>24762299.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.96</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12460</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>37.3</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>96.965</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>154.296</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>42.35</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>41.68000000000001</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.93</v>
+        <v>41.03</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.36</v>
+        <v>41.37</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>260.45</t>
+          <t>1001.86</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-105.17</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6552199.0</t>
+          <t>4122118.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>4776685.6</v>
+        <v>5361259.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3819962.8</t>
+          <t>4066375.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3197880.56</v>
+        <v>3250427.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>956722</t>
+          <t>1294884</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>152296.0942757491</t>
+          <t>201361.1215580679</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>563268.8577191187</t>
+          <t>471218.7716108211</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>6552199.0</t>
+          <t>4122118.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>113.221</t>
+          <t>154.296</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,39 +6189,39 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>41.68000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.86</v>
+        <v>40.93</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.35</v>
+        <v>41.36</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6230,17 +6230,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>134.89</t>
+          <t>260.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.53</t>
+          <t>-105.17</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>3689547.2</v>
+        <v>4776685.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3347516.6</t>
+          <t>3819962.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3114730.64</v>
+        <v>3197880.56</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>342030</t>
+          <t>956722</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>77573.77364968196</t>
+          <t>152296.0942757491</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>414286.4143838617</t>
+          <t>563268.8577191187</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,17 +6426,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>224.845</t>
+          <t>113.221</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-20.60</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.8</v>
+        <v>40.86</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>134.89</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.41</t>
+          <t>-108.53</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3205574.4</v>
+        <v>3689547.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>2945451.4</t>
+          <t>3347516.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3037945.7</v>
+        <v>3114730.64</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>260123</t>
+          <t>342030</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>16353.29351619472</t>
+          <t>77573.77364968196</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>377396.5876769274</t>
+          <t>414286.4143838617</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.809</t>
+          <t>224.845</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-20.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.77</v>
+        <v>40.8</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-111.41</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>1890196.4</v>
+        <v>3205574.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2188136.6</t>
+          <t>2945451.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>2880265.04</v>
+        <v>3037945.7</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-297940</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-49290.9417857567</t>
+          <t>16353.29351619472</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-193793.0428928696</t>
+          <t>377396.5876769274</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.8</v>
+        <v>40.77</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.37</v>
+        <v>41.35</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.03</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2771491.2</v>
+        <v>1890196.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2188645.6</t>
+          <t>2188136.6</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2927231.58</v>
+        <v>2880265.04</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>-297940</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-23017.83249355435</t>
+          <t>-49290.9417857567</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-187411.0850321194</t>
+          <t>-193793.0428928696</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,37 +7894,37 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -7934,28 +7934,28 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.4</v>
+        <v>41.37</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2863240</v>
+        <v>2771491.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3003536.14</v>
+        <v>2927231.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,75 +8324,75 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.43</v>
+        <v>41.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>3005486</v>
+        <v>2863240</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3080321.22</v>
+        <v>3003536.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,68 +8754,68 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.94</v>
+        <v>40.89</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.47</v>
+        <v>41.43</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>2685328.4</v>
+        <v>3005486</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3081600.88</v>
+        <v>3080321.22</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,63 +9184,63 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>40.97</v>
+        <v>40.94</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>2486076.8</v>
+        <v>2685328.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3050572.62</v>
+        <v>3081600.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM22" t="n">
         <v>40.97</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.53</v>
+        <v>41.5</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>1605800</v>
+        <v>2486076.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>2958210.36</v>
+        <v>3050572.62</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.771</t>
+          <t>40.973</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-45.34</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.82</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,37 +10044,37 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>47.83</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>71.01</t>
-        </is>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -10084,28 +10084,28 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.79000000000001</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>41.03</v>
+        <v>40.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.57</v>
+        <v>41.53</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>41.92</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.72</t>
+          <t>-115.80</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11420336.4017094</t>
+          <t>11412886.67283073</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1817978</v>
+        <v>1605800</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2955478.4</t>
+          <t>2937936.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2948865.1</v>
+        <v>2958210.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1137500</t>
+          <t>-1332136</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20480.24477300301</t>
+          <t>-12688.03840258368</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-158638.1234023483</t>
+          <t>-195113.5958683104</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1827737.0</t>
+          <t>1657994.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.38</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>363.213</t>
+          <t>358.496</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-63.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-10.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM2" t="n">
         <v>37.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.78</v>
+        <v>39.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>55.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.37</t>
+          <t>-120.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>21356523.4</v>
+        <v>16966580.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>49229400.6</t>
+          <t>46233081.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>32854915.68</v>
+        <v>32635911.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-27872877</t>
+          <t>-29266501</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>2428375.311425582</t>
+          <t>1373420.579069047</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-3231403.064312473</t>
+          <t>-4428830.448891897</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>39.25</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>510.601</t>
+          <t>492.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.85</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.78</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.01000000000001</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>38.04</v>
+        <v>38</v>
       </c>
       <c r="AN5" t="n">
-        <v>39.97</v>
+        <v>39.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>41.20</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.60</t>
+          <t>-129.55</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>73854919.59999999</v>
+        <v>69426442.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>55863021.8</t>
+          <t>52456837.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33328621.84</v>
+        <v>33433682.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>17991897</t>
+          <t>16969605</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4990346.878352229</t>
+          <t>4345764.102201018</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>3809528.634606227</t>
+          <t>800558.8333693519</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>19953309.0</t>
+          <t>19156578.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.25</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>914.803</t>
+          <t>510.601</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-2.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>38.01000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>38.08</v>
+        <v>38.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>40.03</v>
+        <v>39.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.29</t>
+          <t>-132.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>75499582.59999999</v>
+        <v>73854919.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>55792550.2</t>
+          <t>55863021.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>33454972.78</v>
+        <v>33328621.84</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>19707032</t>
+          <t>17991897</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>5205041.104487866</t>
+          <t>4990346.878352229</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>7886638.29228013</t>
+          <t>3809528.634606227</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>35810040.0</t>
+          <t>19953309.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1043.085</t>
+          <t>914.803</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>35.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.70</t>
+          <t>-9.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,60 +3179,60 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>59.17</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.89</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>37.47</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>38.11</v>
+        <v>38.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>40.07</v>
+        <v>40.03</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>41.23</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>20.99</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-1.00</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>2.69</t>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.15</t>
+          <t>-135.29</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>77102277.8</v>
+        <v>75499582.59999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>54515793.2</t>
+          <t>55792550.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>33864219.92</v>
+        <v>33454972.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>22586484</t>
+          <t>19707032</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4717477.979434728</t>
+          <t>5205041.104487866</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>11730479.54280426</t>
+          <t>7886638.29228013</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>39561838.0</t>
+          <t>35810040.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6301.223</t>
+          <t>1043.085</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-14.48</t>
+          <t>-11.70</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>59.17</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-4.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.60000000000001</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>38.22</v>
+        <v>38.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.17</v>
+        <v>40.07</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>41.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>5.10</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.62</t>
+          <t>-137.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>74142370</v>
+        <v>77102277.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>57245793.0</t>
+          <t>54515793.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>34130931.06</v>
+        <v>33864219.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16896577</t>
+          <t>22586484</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3442386.786094812</t>
+          <t>4717477.979434728</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>16400757.27416717</t>
+          <t>11730479.54280426</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>232650449.0</t>
+          <t>39561838.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.08</t>
+          <t>-8.19</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>37.05</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>37.0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>37.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>36.9</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1128.761</t>
+          <t>6301.223</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-14.60</t>
+          <t>-14.48</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>67.14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,274 +4024,274 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>-4.24</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>-4.85</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>36.60000000000001</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>41.28</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-7.24</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.69</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-137.62</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/25</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>149536314.334517</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>74142370</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>57245793.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>34130931.06</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>16896577</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>3442386.786094812</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>16400757.27416717</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>232650449.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-11.08</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>新光鋼</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-13.67996844119094</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-10.11024290164889</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>24.12947661306339</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>6.46</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>11.90</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>15.99</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>8.69%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>12428</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>新光鋼-鋼鐵工業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>鋼鐵工業右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.66</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-4.68</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>-4.69</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>-2.48</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>41.32</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-12.91</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.69</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-136.94</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/25</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>149719452.0704125</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>35487232</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>35914543.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>29950115.64</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-427311</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>1086319.424627111</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>1798775.809179619</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>41298962.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-11.20</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>新光鋼</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-13.67996844119094</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-10.11024290164889</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>24.12947661306339</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.44</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>11.90</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>16.05</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>8.69%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>5.19%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>30.23</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>12477</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>鋼板38.80%、熱軋及鍍鋅鋼板33.80%、不�袗�板12.60%、特殊鋼板7.00%、加工及其他6.90%、型鋼0.90% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>新光鋼-鋼鐵工業-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>鋼鐵工業右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>36.4</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>36.95</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>776.396</t>
+          <t>1128.761</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-15.64</t>
+          <t>-14.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.73</t>
+          <t>36.61</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>38.6</v>
+        <v>38.41</v>
       </c>
       <c r="AN10" t="n">
-        <v>40.43</v>
+        <v>40.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.75</t>
+          <t>-136.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>37871124</v>
+        <v>35487232</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>34509118.0</t>
+          <t>35914543.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>29545425.32</v>
+        <v>29950115.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3362006</t>
+          <t>-427311</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>956781.9001630185</t>
+          <t>1086319.424627111</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1376505.330298137</t>
+          <t>1798775.809179619</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>28176624.0</t>
+          <t>41298962.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-12.29</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1212.053</t>
+          <t>776.396</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-16.34</t>
+          <t>-15.64</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.07000000000001</t>
+          <t>36.73</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>40.58</v>
+        <v>40.43</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>41.39</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.07</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-134.02</t>
+          <t>-135.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>36085517.8</v>
+        <v>37871124</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>35025550.9</t>
+          <t>34509118.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>29409986</v>
+        <v>29545425.32</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1059966</t>
+          <t>3362006</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>880468.5492293607</t>
+          <t>956781.9001630185</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2130065.670099653</t>
+          <t>1376505.330298137</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>43823516.0</t>
+          <t>28176624.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>672.504</t>
+          <t>1212.053</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-16.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.97</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.47000000000001</t>
+          <t>37.07000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>39.02</v>
+        <v>38.8</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.75</v>
+        <v>40.58</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>41.45</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-22.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>149719452.0704125</t>
+          <t>149536314.334517</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>31929308.6</v>
+        <v>36085517.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>32595150.7</t>
+          <t>35025550.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>29130934.74</v>
+        <v>29409986</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-665842</t>
+          <t>1059966</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>653269.0727074891</t>
+          <t>880468.5492293607</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1454053.953026839</t>
+          <t>2130065.670099653</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>24762299.0</t>
+          <t>43823516.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>96.965</t>
+          <t>41.031</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5764,53 +5764,53 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>42.36</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>41.03</v>
+        <v>41.15</v>
       </c>
       <c r="AN13" t="n">
-        <v>41.37</v>
+        <v>41.38</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>41.73</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>1001.86</t>
+          <t>663.99</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-101.47</t>
+          <t>-97.77</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4122118.0</t>
+          <t>1747189.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>5361259.2</v>
+        <v>5335779.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4066375.2</t>
+          <t>3612988.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3250427.38</v>
+        <v>2889481.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>1294884</t>
+          <t>1722791</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>201361.1215580679</t>
+          <t>203749.1900944794</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>471218.7716108211</t>
+          <t>216883.5670447429</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>4122118.0</t>
+          <t>1747189.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,34 +6043,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>96.965</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>42.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>154.296</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>42.35</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.05</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>41.68000000000001</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>40.93</v>
+        <v>41.03</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.36</v>
+        <v>41.37</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>260.45</t>
+          <t>1001.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.17</t>
+          <t>-101.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6552199.0</t>
+          <t>4122118.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>4776685.6</v>
+        <v>5361259.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3819962.8</t>
+          <t>4066375.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3197880.56</v>
+        <v>3250427.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>956722</t>
+          <t>1294884</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>152296.0942757491</t>
+          <t>201361.1215580679</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>563268.8577191187</t>
+          <t>471218.7716108211</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6552199.0</t>
+          <t>4122118.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>113.221</t>
+          <t>154.296</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,39 +6619,39 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>41.68000000000001</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>40.86</v>
+        <v>40.93</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.35</v>
+        <v>41.36</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6660,17 +6660,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>134.89</t>
+          <t>260.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.53</t>
+          <t>-105.17</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>3689547.2</v>
+        <v>4776685.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3347516.6</t>
+          <t>3819962.8</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3114730.64</v>
+        <v>3197880.56</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>342030</t>
+          <t>956722</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>77573.77364968196</t>
+          <t>152296.0942757491</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>414286.4143838617</t>
+          <t>563268.8577191187</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4771976.0</t>
+          <t>6552199.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>224.845</t>
+          <t>113.221</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-20.60</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11.56</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7049,58 +7049,58 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>40.8</v>
+        <v>40.86</v>
       </c>
       <c r="AN16" t="n">
-        <v>41.34</v>
+        <v>41.35</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>66.27</t>
+          <t>134.89</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.41</t>
+          <t>-108.53</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3205574.4</v>
+        <v>3689547.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2945451.4</t>
+          <t>3347516.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3037945.7</v>
+        <v>3114730.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>260123</t>
+          <t>342030</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>16353.29351619472</t>
+          <t>77573.77364968196</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>377396.5876769274</t>
+          <t>414286.4143838617</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>9485416.0</t>
+          <t>4771976.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.809</t>
+          <t>224.845</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-22.50</t>
+          <t>-20.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,68 +7469,68 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>40.77</v>
+        <v>40.8</v>
       </c>
       <c r="AN17" t="n">
-        <v>41.35</v>
+        <v>41.34</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>41.76</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>66.27</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.30</t>
+          <t>-111.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>1890196.4</v>
+        <v>3205574.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2188136.6</t>
+          <t>2945451.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>2880265.04</v>
+        <v>3037945.7</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-297940</t>
+          <t>260123</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-49290.9417857567</t>
+          <t>16353.29351619472</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-193793.0428928696</t>
+          <t>377396.5876769274</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1874587.0</t>
+          <t>9485416.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.504</t>
+          <t>45.809</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-23.06</t>
+          <t>-22.50</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,68 +7899,68 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-1.00</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>40.67</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>40.8</v>
+        <v>40.77</v>
       </c>
       <c r="AN18" t="n">
-        <v>41.37</v>
+        <v>41.35</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>21.72</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.03</t>
+          <t>-113.30</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2771491.2</v>
+        <v>1890196.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>2188645.6</t>
+          <t>2188136.6</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>2927231.58</v>
+        <v>2880265.04</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>582845</t>
+          <t>-297940</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-23017.83249355435</t>
+          <t>-49290.9417857567</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-187411.0850321194</t>
+          <t>-193793.0428928696</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1199250.0</t>
+          <t>1874587.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-5.13</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.554</t>
+          <t>29.504</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-23.25</t>
+          <t>-23.06</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,32 +8329,32 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>29.63</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -8364,28 +8364,28 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>40.63</t>
+          <t>40.71</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>40.84</v>
+        <v>40.8</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.4</v>
+        <v>41.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.37</t>
+          <t>-114.03</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>2863240</v>
+        <v>2771491.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2340609.0</t>
+          <t>2188645.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3003536.14</v>
+        <v>2927231.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>522631</t>
+          <t>582845</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>6871.849786184752</t>
+          <t>-23017.83249355435</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-99243.2136227577</t>
+          <t>-187411.0850321194</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1116507.0</t>
+          <t>1199250.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.36</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57.95</t>
+          <t>27.554</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-23.63</t>
+          <t>-23.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,70 +8759,70 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>40.63</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>40.89</v>
+        <v>40.84</v>
       </c>
       <c r="AN20" t="n">
-        <v>41.43</v>
+        <v>41.4</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.24</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>1.7</t>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.58</t>
+          <t>-114.37</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3005486</v>
+        <v>2863240</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3079622.6</t>
+          <t>2340609.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3080321.22</v>
+        <v>3003536.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-74136</t>
+          <t>522631</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>26165.49767871974</t>
+          <t>6871.849786184752</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>39120.61030571489</t>
+          <t>-99243.2136227577</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>2352112.0</t>
+          <t>1116507.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-5.36</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>71.306</t>
+          <t>57.95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-23.16</t>
+          <t>-23.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,63 +9189,63 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>52.25</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>40.76000000000001</t>
+          <t>40.64</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>40.94</v>
+        <v>40.89</v>
       </c>
       <c r="AN21" t="n">
-        <v>41.47</v>
+        <v>41.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>41.84</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.76</t>
+          <t>-114.58</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>2685328.4</v>
+        <v>3005486</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3111515.3</t>
+          <t>3079622.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3081600.88</v>
+        <v>3080321.22</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-426186</t>
+          <t>-74136</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>23810.02265562972</t>
+          <t>26165.49767871974</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>102999.801264043</t>
+          <t>39120.61030571489</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>2908526.0</t>
+          <t>2352112.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>153.739</t>
+          <t>71.306</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.63</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>-23.16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,58 +9619,58 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>95.65</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>54.35</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>40.76000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>40.97</v>
+        <v>40.94</v>
       </c>
       <c r="AN22" t="n">
-        <v>41.5</v>
+        <v>41.47</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>41.87</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-115.22</t>
+          <t>-114.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>2486076.8</v>
+        <v>2685328.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3055097.0</t>
+          <t>3111515.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>3050572.62</v>
+        <v>3081600.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-569020</t>
+          <t>-426186</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>9411.881090463668</t>
+          <t>23810.02265562972</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>130961.438302224</t>
+          <t>102999.801264043</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>6281061.0</t>
+          <t>2908526.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>40.973</t>
+          <t>153.739</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-45.34</t>
+          <t>-18.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-23.82</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>95.65</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>53.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>40.97</v>
       </c>
       <c r="AN23" t="n">
-        <v>41.53</v>
+        <v>41.5</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>41.92</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>15.02</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-115.80</t>
+          <t>-115.22</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>11412886.67283073</t>
+          <t>11400397.88991477</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>1605800</v>
+        <v>2486076.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2937936.4</t>
+          <t>3055097.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>2958210.36</v>
+        <v>3050572.62</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1332136</t>
+          <t>-569020</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-12688.03840258368</t>
+          <t>9411.881090463668</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-195113.5958683104</t>
+          <t>130961.438302224</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1657994.0</t>
+          <t>6281061.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/鋼材.xlsx
+++ b/Result/checksun_type/鋼材.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>358.496</t>
+          <t>435.235</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-63.30</t>
+          <t>-63.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.31</t>
+          <t>-9.50</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>435</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>82.22</t>
+          <t>97.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.65</t>
+          <t>90.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.37</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>38.86</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>37.97</v>
+        <v>37.98</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.7</v>
+        <v>39.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>55.74</t>
+          <t>63.94</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-120.51</t>
+          <t>-117.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>149536314.334517</t>
+          <t>149360369.7340426</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>16966580.2</v>
+        <v>16375301.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>46233081.4</t>
+          <t>45115110.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>32635911.38</v>
+        <v>32578634.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29266501</t>
+          <t>-28739809</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1373420.579069047</t>
+          <t>405038.2427699324</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-4428830.448891897</t>
+          <t>-4921064.606875196</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13860324.0</t>
+          <t>16996914.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-6.75</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>38.7</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>39.05</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>39.1</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>38.45</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>38.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>363.213</t>
+          <t>358.496</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-56.62</t>
+          <t>-63.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-10.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>435</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>82.22</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>87.65</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.56</t>
+          <t>-4.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>37.97</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.78</v>
+        <v>39.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>55.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.37</t>
+          <t>-120.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>149536314.334517</t>
+          <t>149360369.7340426</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>21356523.4</v>
+        <v>16966580.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>49229400.6</t>
+          <t>46233081.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>32854915.68</v>
+        <v>32635911.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-27872877</t>
+          <t>-29266501</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>2428375.311425582</t>
+          <t>1373420.579069047</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-3231403.064312473</t>
+          <t>-4428830.448891897</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14075446.0</t>
+          <t>13860324.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-6.75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>38.6</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>455.261</t>
+          <t>363.213</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-47.41</t>
+          <t>-56.62</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>435</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>91.36</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-4.56</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.95</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>37.98</v>
+        <v>37.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>41.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-126.44</t>
+          <t>-123.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>149536314.334517</t>
+          <t>149360369.7340426</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>26453801.8</v>
+        <v>21356523.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>50298085.9</t>
+          <t>49229400.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>33264214.78</v>
+        <v>32854915.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-23844284</t>
+          <t>-27872877</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3457425.925196137</t>
+          <t>2428375.311425582</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1428434.048330702</t>
+          <t>-3231403.064312473</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>17787244.0</t>
+          <t>14075446.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>38.95</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>38.6</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.8</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>492.79</t>
+          <t>455.261</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>-47.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.85</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>435</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>97.78</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>38.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>38</v>
+        <v>37.98</v>
       </c>
       <c r="AN5" t="n">
-        <v>39.92</v>
+        <v>39.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>41.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>41.20</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.55</t>
+          <t>-126.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>149536314.334517</t>
+          <t>149360369.7340426</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>69426442.8</v>
+        <v>26453801.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>52456837.4</t>
+          <t>50298085.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>33433682.52</v>
+        <v>33264214.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>16969605</t>
+          <t>-23844284</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4345764.102201018</t>
+          <t>3457425.925196137</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>800558.8333693519</t>
+          <t>-1428434.048330702</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>19156578.0</t>
+          <t>17787244.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.51</t>
        